--- a/outputs/daily/hr_rankings_2026-08-18_remaining.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-18_remaining.xlsx
@@ -1666,34 +1666,30 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4470,34 +4466,30 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -15954,34 +15946,30 @@
       </c>
       <c r="W56" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y56" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB56" t="inlineStr"/>
       <c r="AC56" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -19878,34 +19866,30 @@
       </c>
       <c r="W70" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X70" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y70" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB70" t="inlineStr"/>
       <c r="AC70" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -27998,34 +27982,30 @@
       </c>
       <c r="W99" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X99" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y99" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB99" t="inlineStr"/>
       <c r="AC99" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -39202,34 +39182,30 @@
       </c>
       <c r="W139" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X139" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z139" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X139" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y139" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z139" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB139" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 6</t>
-        </is>
-      </c>
+      <c r="AB139" t="inlineStr"/>
       <c r="AC139" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -41166,34 +41142,30 @@
       </c>
       <c r="W146" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X146" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z146" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X146" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y146" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z146" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA146" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB146" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB146" t="inlineStr"/>
       <c r="AC146" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -41730,34 +41702,30 @@
       </c>
       <c r="W148" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X148" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z148" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X148" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y148" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z148" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB148" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 7</t>
-        </is>
-      </c>
+      <c r="AB148" t="inlineStr"/>
       <c r="AC148" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -44250,34 +44218,30 @@
       </c>
       <c r="W157" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X157" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z157" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X157" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y157" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z157" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB157" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB157" t="inlineStr"/>
       <c r="AC157" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -77592,34 +77556,30 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -80396,34 +80356,30 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>

--- a/outputs/daily/hr_rankings_2026-08-18_remaining.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-18_remaining.xlsx
@@ -1040,7 +1040,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -5800,7 +5800,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -7200,7 +7200,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -8040,7 +8040,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -8600,7 +8600,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -8880,7 +8880,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -9160,7 +9160,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -9440,7 +9440,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -9720,7 +9720,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -10000,7 +10000,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -10560,7 +10560,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -10840,7 +10840,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -11400,7 +11400,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -11960,7 +11960,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -13080,7 +13080,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -15040,7 +15040,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -15320,7 +15320,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -15600,7 +15600,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -15880,7 +15880,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -16160,7 +16160,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -16440,7 +16440,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -16720,7 +16720,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -17280,7 +17280,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -17560,7 +17560,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -17840,7 +17840,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -18120,7 +18120,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -20080,7 +20080,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -21526,7 +21526,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -22086,7 +22086,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -22646,7 +22646,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -22926,7 +22926,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -23206,7 +23206,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -23486,7 +23486,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -24046,7 +24046,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -24326,7 +24326,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -26006,7 +26006,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -26286,7 +26286,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
